--- a/src/excels/hàng xln -.xlsx
+++ b/src/excels/hàng xln -.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134E688D-ECA0-428B-BAC3-7A7B60389F24}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2968FE26-E041-4E06-AB73-E7B380729333}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="530" xr2:uid="{FF3FD4B8-14B6-4378-8FF4-8519CEF95A47}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Hàng xln'!$4:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'xử lý chất liệu'!$1:$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
